--- a/tools/fii-flows/FII_FPI_Historical_Data_India.xlsx
+++ b/tools/fii-flows/FII_FPI_Historical_Data_India.xlsx
@@ -1098,16 +1098,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-93319</v>
+        <v>-129180</v>
       </c>
       <c r="C36" t="n">
-        <v>63142</v>
+        <v>40560</v>
       </c>
       <c r="D36" t="n">
-        <v>-30177</v>
+        <v>-88620</v>
       </c>
       <c r="E36" t="n">
-        <v>1454226</v>
+        <v>1395783</v>
       </c>
     </row>
   </sheetData>
@@ -1564,16 +1564,16 @@
         <v>2026</v>
       </c>
       <c r="B26" t="n">
-        <v>-224441</v>
+        <v>-260302</v>
       </c>
       <c r="C26" t="n">
-        <v>77092</v>
+        <v>54510</v>
       </c>
       <c r="D26" t="n">
-        <v>-147349</v>
+        <v>-205792</v>
       </c>
       <c r="E26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1587,7 +1587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C297"/>
+  <dimension ref="A1:C298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5455,6 +5455,19 @@
         <v>25492</v>
       </c>
     </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>-35861</v>
+      </c>
+      <c r="C298" t="n">
+        <v>-58443</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
